--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487127_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487127_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5918</v>
+        <v>4.0425</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2607</v>
+        <v>3.4973</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3311</v>
+        <v>0.5453</v>
       </c>
       <c r="G2" t="n">
         <v>1.8075</v>
@@ -610,13 +610,13 @@
         <v>3.6672</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6842</v>
+        <v>1.1349</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6724</v>
+        <v>0.9089</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0119</v>
+        <v>0.226</v>
       </c>
       <c r="V2" t="n">
         <v>0.3281</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5871</v>
+        <v>3.7933</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1125</v>
+        <v>2.8904</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4746</v>
+        <v>0.9029</v>
       </c>
       <c r="G3" t="n">
         <v>1.9942</v>
@@ -688,13 +688,13 @@
         <v>2.5091</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4614</v>
+        <v>0.6676</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.472</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2327</v>
+        <v>0.1956</v>
       </c>
       <c r="V3" t="n">
         <v>-0.4126</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9312</v>
+        <v>1.3651</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.9969</v>
+        <v>-2.5994</v>
       </c>
       <c r="F4" t="n">
-        <v>4.9282</v>
+        <v>3.9645</v>
       </c>
       <c r="G4" t="n">
         <v>-2.0832</v>
@@ -766,13 +766,13 @@
         <v>3.8602</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7807</v>
+        <v>1.2146</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0198</v>
+        <v>0.3778</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8004</v>
+        <v>0.8367</v>
       </c>
       <c r="V4" t="n">
         <v>2.2337</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. TRUEBA TAMAYO</t>
+          <t>M. CARCOBA BEDIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4068</v>
+        <v>0.2428</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7892</v>
+        <v>-2.7948</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3825</v>
+        <v>3.0376</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8747</v>
+        <v>-1.3677</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.925</v>
+        <v>-0.0539</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0503</v>
+        <v>-1.3138</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4006</v>
+        <v>-1.5483</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5227000000000001</v>
+        <v>0.4138</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1221</v>
+        <v>-1.9621</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4741</v>
+        <v>0.1806</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4023</v>
+        <v>-0.4677</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9282</v>
+        <v>0.6483</v>
       </c>
       <c r="P5" t="n">
-        <v>0.193</v>
+        <v>2.5091</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>1.158</v>
+        <v>3.4741</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5757</v>
+        <v>0.4521</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5764</v>
+        <v>0.3748</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0007</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3008</v>
+        <v>-1.3508</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3008</v>
+        <v>-0.6945</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SANCHEZ MARROYO</t>
+          <t>D. TRUEBA TAMAYO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6871</v>
+        <v>-0.4554</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0165</v>
+        <v>-0.8111</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7035</v>
+        <v>0.3557</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.159</v>
+        <v>-0.8747</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3332</v>
+        <v>-1.925</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1742</v>
+        <v>1.0503</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0614</v>
+        <v>-0.4006</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0207</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0407</v>
+        <v>0.1221</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2204</v>
+        <v>-0.4741</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3539</v>
+        <v>-1.4023</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1335</v>
+        <v>0.9282</v>
       </c>
       <c r="P6" t="n">
         <v>0.193</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>0.193</v>
+        <v>1.158</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1071</v>
+        <v>0.5271</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0449</v>
+        <v>0.5546</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0621</v>
+        <v>-0.0275</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.614</v>
+        <v>-0.3008</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.614</v>
+        <v>-0.3008</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. CARCOBA BEDIA</t>
+          <t>J. SANCHEZ MARROYO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-0.4798</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.9747</v>
+        <v>0.1166</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0911</v>
+        <v>-0.5964</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3677</v>
+        <v>-0.159</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0539</v>
+        <v>-0.3332</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3138</v>
+        <v>0.1742</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5483</v>
+        <v>0.0614</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4138</v>
+        <v>0.0207</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.9621</v>
+        <v>0.0407</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1806</v>
+        <v>-0.2204</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4677</v>
+        <v>-0.3539</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6483</v>
+        <v>0.1335</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5091</v>
+        <v>0.193</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.4741</v>
+        <v>0.193</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6742</v>
+        <v>0.1001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.805</v>
+        <v>0.0552</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1308</v>
+        <v>0.0449</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3508</v>
+        <v>-0.614</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6945</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GOMEZ MERODIO</t>
+          <t>L. MAESTRO STEELE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6913</v>
+        <v>-1.6093</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5536</v>
+        <v>-3.2641</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1377</v>
+        <v>1.6548</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.2367</v>
+        <v>-0.2824</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.1535</v>
+        <v>-1.7947</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9167999999999999</v>
+        <v>1.5123</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.8226</v>
+        <v>-0.3488</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.9447</v>
+        <v>-0.9265</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1221</v>
+        <v>0.5777</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4141</v>
+        <v>0.0664</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2087</v>
+        <v>-0.8682</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7947</v>
+        <v>0.9346</v>
       </c>
       <c r="P8" t="n">
-        <v>0.579</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2671</v>
+        <v>0.4128</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0061</v>
+        <v>-0.0201</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2611</v>
+        <v>0.4329</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3008</v>
+        <v>0.1904</v>
       </c>
       <c r="W8" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5288</v>
+        <v>0.1904</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. MAESTRO STEELE</t>
+          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.116</v>
+        <v>-1.8906</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.8243</v>
+        <v>-4.5332</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7083</v>
+        <v>2.6426</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2824</v>
+        <v>-2.0073</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7947</v>
+        <v>-1.1769</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5123</v>
+        <v>-0.8304</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3488</v>
+        <v>-2.0142</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9265</v>
+        <v>-0.6626</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5777</v>
+        <v>-1.3516</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0664</v>
+        <v>0.0069</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8682</v>
+        <v>-0.5143</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9346</v>
+        <v>0.5212</v>
       </c>
       <c r="P9" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-1.9301</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-2.8951</v>
-      </c>
       <c r="R9" t="n">
-        <v>0.965</v>
+        <v>2.5091</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0939</v>
+        <v>-0.424</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5803</v>
+        <v>-0.5889</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4865</v>
+        <v>0.1649</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1904</v>
+        <v>-0.0383</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1904</v>
+        <v>-0.0383</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
+          <t>J. GOMEZ MERODIO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9584</v>
+        <v>-2.3943</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.253</v>
+        <v>-2.1763</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2946</v>
+        <v>-0.218</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0073</v>
+        <v>-3.2367</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1769</v>
+        <v>-4.1535</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8304</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0142</v>
+        <v>-2.8226</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6626</v>
+        <v>-2.9447</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3516</v>
+        <v>0.1221</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0069</v>
+        <v>-0.4141</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5143</v>
+        <v>-1.2087</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5212</v>
+        <v>0.7947</v>
       </c>
       <c r="P10" t="n">
         <v>0.579</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5091</v>
+        <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4918</v>
+        <v>0.5642</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3087</v>
+        <v>0.3834</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1831</v>
+        <v>0.1807</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.0383</v>
+        <v>-0.3008</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.0383</v>
+        <v>-1.5288</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7831</v>
+        <v>-3.5432</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8953</v>
+        <v>-2.7357</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8878</v>
+        <v>-0.8075</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4696</v>
@@ -1312,13 +1312,13 @@
         <v>0.386</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3616</v>
+        <v>-0.1216</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4759</v>
+        <v>-0.3163</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1143</v>
+        <v>0.1946</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4079</v>
@@ -1345,28 +1345,28 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4162</v>
+        <v>-0.9289000000000005</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.8973</v>
+        <v>-12.4103</v>
       </c>
       <c r="F12" t="n">
-        <v>11.4814</v>
+        <v>11.4815</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.6789</v>
+        <v>-6.678899999999999</v>
       </c>
       <c r="H12" t="n">
         <v>-14.0867</v>
       </c>
       <c r="I12" t="n">
-        <v>7.407899999999999</v>
+        <v>7.4079</v>
       </c>
       <c r="J12" t="n">
         <v>-5.911100000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.0692</v>
+        <v>-4.069199999999999</v>
       </c>
       <c r="L12" t="n">
         <v>-1.8419</v>
@@ -1390,13 +1390,13 @@
         <v>20.2658</v>
       </c>
       <c r="S12" t="n">
-        <v>3.040499999999999</v>
+        <v>4.5278</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7144000000000001</v>
+        <v>2.2014</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3264</v>
+        <v>2.3261</v>
       </c>
       <c r="V12" t="n">
         <v>-1.673</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.3856</v>
+        <v>4.1697</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3576</v>
+        <v>1.3562</v>
       </c>
       <c r="F13" t="n">
-        <v>3.028</v>
+        <v>2.8135</v>
       </c>
       <c r="G13" t="n">
         <v>5.0202</v>
@@ -1468,13 +1468,13 @@
         <v>1.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9215</v>
+        <v>0.7056</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8276</v>
+        <v>-0.1738</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0939</v>
+        <v>0.8794</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5561</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.333</v>
+        <v>2.4843</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2778</v>
+        <v>-0.7785</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6109</v>
+        <v>3.2629</v>
       </c>
       <c r="G14" t="n">
         <v>-2.118</v>
@@ -1546,13 +1546,13 @@
         <v>2.7021</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3425</v>
+        <v>0.4938</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.0149</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8268</v>
+        <v>0.4788</v>
       </c>
       <c r="V14" t="n">
         <v>2.3714</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6173</v>
+        <v>1.0526</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.3249</v>
+        <v>-1.4251</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9423</v>
+        <v>2.4776</v>
       </c>
       <c r="G15" t="n">
         <v>0.999</v>
@@ -1624,13 +1624,13 @@
         <v>2.5091</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2393</v>
+        <v>0.196</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.078</v>
+        <v>-0.1781</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1613</v>
+        <v>0.3741</v>
       </c>
       <c r="V15" t="n">
         <v>0.2436</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4977</v>
+        <v>0.2697</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1321</v>
+        <v>0.3324</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3656</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>1.8167</v>
@@ -1702,13 +1702,13 @@
         <v>1.5441</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2538</v>
+        <v>-0.4819</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2697</v>
+        <v>-0.0694</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0158</v>
+        <v>-0.4125</v>
       </c>
       <c r="V16" t="n">
         <v>0.2859</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2344</v>
+        <v>0.1679</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.536</v>
+        <v>-0.7362</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7703</v>
+        <v>0.9042</v>
       </c>
       <c r="G17" t="n">
         <v>0.7357</v>
@@ -1780,13 +1780,13 @@
         <v>1.5441</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4012</v>
+        <v>-0.4676</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1005</v>
+        <v>-0.0998</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5017</v>
+        <v>-0.3679</v>
       </c>
       <c r="V17" t="n">
         <v>0.2859</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0854</v>
+        <v>0.0611</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.956</v>
+        <v>-0.7557</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8706</v>
+        <v>0.8168</v>
       </c>
       <c r="G18" t="n">
         <v>1.5958</v>
@@ -1858,13 +1858,13 @@
         <v>0.772</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1177</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5354</v>
+        <v>-0.3351</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5824</v>
+        <v>-0.6362</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3704</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>E. ERRASTI DIEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6793</v>
+        <v>-0.6532</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5342</v>
+        <v>-3.7858</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1451</v>
+        <v>3.1327</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3854</v>
+        <v>-1.6939</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0961</v>
+        <v>0.9615</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4816</v>
+        <v>-2.6554</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8798</v>
+        <v>-2.1952</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4554</v>
+        <v>0.4345</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3352</v>
+        <v>-2.6297</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4944</v>
+        <v>0.5013</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6408</v>
+        <v>0.527</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1464</v>
+        <v>-0.0257</v>
       </c>
       <c r="P19" t="n">
-        <v>0.965</v>
+        <v>-3.4741</v>
       </c>
       <c r="Q19" t="n">
+        <v>-5.7902</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.3161</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.3969</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.7122000000000001</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.9119</v>
+      </c>
+      <c r="W19" t="n">
+        <v>4.9119</v>
+      </c>
+      <c r="X19" t="n">
         <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-1.4013</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-0.6544</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-0.7469</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-0.8576</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-0.8576</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. CHACON RODRIGUEZ</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7068</v>
+        <v>-1.0312</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3439</v>
+        <v>-1.2338</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6371</v>
+        <v>0.2026</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0592</v>
+        <v>-0.3854</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3198</v>
+        <v>1.0961</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2606</v>
+        <v>-1.4816</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1541</v>
+        <v>-0.8798</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4865</v>
+        <v>0.4554</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6676</v>
+        <v>-1.3352</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0949</v>
+        <v>0.4944</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1667</v>
+        <v>0.6408</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9282</v>
+        <v>-0.1464</v>
       </c>
       <c r="P20" t="n">
         <v>0.965</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9301</v>
+        <v>0.965</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.199</v>
+        <v>-0.7532</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2247</v>
+        <v>-0.3539</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0258</v>
+        <v>-0.3993</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4137</v>
+        <v>-0.8576</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4137</v>
+        <v>-0.8576</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. ERRASTI DIEZ</t>
+          <t>I. CHACON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7553</v>
+        <v>-1.493</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.4868</v>
+        <v>-2.3439</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7314</v>
+        <v>0.8509</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6939</v>
+        <v>-0.0592</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9615</v>
+        <v>-0.3198</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.6554</v>
+        <v>0.2606</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.1952</v>
+        <v>-1.1541</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4345</v>
+        <v>-0.4865</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.6297</v>
+        <v>-0.6676</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5013</v>
+        <v>1.0949</v>
       </c>
       <c r="N21" t="n">
-        <v>0.527</v>
+        <v>0.1667</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0257</v>
+        <v>0.9282</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.4741</v>
+        <v>0.965</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.7902</v>
+        <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3161</v>
+        <v>1.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4991</v>
+        <v>0.0149</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4132</v>
+        <v>-0.2247</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.08599999999999999</v>
+        <v>0.2396</v>
       </c>
       <c r="V21" t="n">
-        <v>4.9119</v>
+        <v>-2.4137</v>
       </c>
       <c r="W21" t="n">
-        <v>4.9119</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.4137</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4251</v>
+        <v>-1.9442</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5114</v>
+        <v>-2.1108</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0863</v>
+        <v>0.1666</v>
       </c>
       <c r="G22" t="n">
         <v>0.768</v>
@@ -2170,13 +2170,13 @@
         <v>1.158</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1931</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5949</v>
+        <v>-0.1943</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5982</v>
+        <v>-0.5179</v>
       </c>
       <c r="V22" t="n">
         <v>-1.228</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.416100000000001</v>
+        <v>3.0837</v>
       </c>
       <c r="E23" t="n">
-        <v>-11.4813</v>
+        <v>-11.4812</v>
       </c>
       <c r="F23" t="n">
-        <v>13.8974</v>
+        <v>14.5651</v>
       </c>
       <c r="G23" t="n">
         <v>6.678900000000001</v>
@@ -2221,7 +2221,7 @@
         <v>-7.408</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7676999999999999</v>
+        <v>0.7677000000000002</v>
       </c>
       <c r="K23" t="n">
         <v>10.0176</v>
@@ -2230,10 +2230,10 @@
         <v>-9.2498</v>
       </c>
       <c r="M23" t="n">
-        <v>5.911299999999999</v>
+        <v>5.911300000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>4.069100000000001</v>
+        <v>4.0691</v>
       </c>
       <c r="O23" t="n">
         <v>1.842</v>
@@ -2248,13 +2248,13 @@
         <v>17.3707</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.0405</v>
+        <v>-2.3728</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.3266</v>
+        <v>-2.3264</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.04669999999999996</v>
       </c>
       <c r="V23" t="n">
         <v>1.6729</v>
